--- a/multifleet_solveD_examaples.xlsx
+++ b/multifleet_solveD_examaples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Fork_fish_Sim_GTG\fishSimGTG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B1A928B6-EFFA-4CC0-A2F9-C01BABAFAC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7C6AB4-7680-4D9F-923E-C00FE170846C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{5B2CD74D-F7F8-4780-BA30-98A72E2573DE}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B2CD74D-F7F8-4780-BA30-98A72E2573DE}"/>
   </bookViews>
   <sheets>
     <sheet name="multifleet_solveD_examaples" sheetId="1" r:id="rId1"/>
@@ -666,7 +666,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -678,26 +678,14 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -714,6 +702,19 @@
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1093,52 +1094,54 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="5" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.3984375" customWidth="1"/>
-    <col min="7" max="7" width="11.73046875" customWidth="1"/>
-    <col min="8" max="9" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.3984375" customWidth="1"/>
-    <col min="11" max="12" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.796875" customWidth="1"/>
+    <col min="3" max="3" width="16.3984375" customWidth="1"/>
+    <col min="4" max="4" width="12.1328125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" customWidth="1"/>
+    <col min="7" max="7" width="14.3984375" customWidth="1"/>
+    <col min="8" max="9" width="14.265625" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.73046875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="26" t="s">
         <v>23</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="26" t="s">
         <v>25</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="16" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1149,37 +1152,37 @@
       <c r="B2" s="3">
         <v>0.2</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>0.2</v>
       </c>
       <c r="D2" s="3">
         <v>6.2E-2</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>6.2E-2</v>
       </c>
       <c r="F2" s="3">
         <v>0.2</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>0.2</v>
       </c>
       <c r="H2" s="3">
         <v>6.2E-2</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>6.2E-2</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="9">
         <v>0.2</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="10">
         <v>6.3E-2</v>
       </c>
-      <c r="L2" s="15">
+      <c r="L2" s="11">
         <v>6.3E-2</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="12">
         <v>6.2E-2</v>
       </c>
     </row>
@@ -1190,37 +1193,37 @@
       <c r="B3" s="3">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D3" s="3">
         <v>0.4</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>0.4</v>
       </c>
       <c r="F3" s="3">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="H3" s="3">
         <v>0.4</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>0.4</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="25">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="10">
         <v>0.4</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="11">
         <v>0.4</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="12">
         <v>0.4</v>
       </c>
     </row>
@@ -1231,37 +1234,37 @@
       <c r="B4" s="3">
         <v>7984550.6299999999</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>7984550.6299999999</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>7984550.6299999999</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>7984550.6299999999</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>7984550.6299999999</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>7984550.6299999999</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>7984550.6299999999</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>7984550.6299999999</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="9">
         <v>7984550.6299999999</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="10">
         <v>7984550.6299999999</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="11">
         <v>7984550.6299999999</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="12">
         <v>7984550.6299999999</v>
       </c>
     </row>
@@ -1272,37 +1275,37 @@
       <c r="B5" s="3">
         <v>276879.59100000001</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>276879.59100000001</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>3193820.2519999999</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>3193820.2519999999</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>276879.59100000001</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>276879.59100000001</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>3193820.2519999999</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>3193820.2519999999</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="9">
         <v>347831.76</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="13">
         <v>3193820.236</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="14">
         <v>3193820.2179999999</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="15">
         <v>3193820.2519999999</v>
       </c>
     </row>
@@ -1313,37 +1316,37 @@
       <c r="B6" s="3">
         <v>531424.87300000002</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>531424.87300000002</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>6268729.273</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>6268729.273</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>531424.87300000002</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>531424.87300000002</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>6268729.273</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>6268729.273</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="9">
         <v>657084.00699999998</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="13">
         <v>6218363.2709999997</v>
       </c>
-      <c r="L6" s="18">
+      <c r="L6" s="14">
         <v>6198113.5829999996</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="15">
         <v>6232160.0539999995</v>
       </c>
     </row>
@@ -1354,37 +1357,37 @@
       <c r="B7" s="3">
         <v>0.24</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="17">
         <v>0.24</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="20">
         <v>0.52800000000000002</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="21">
         <v>0.52800000000000002</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="18">
         <v>0.24</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="17">
         <v>0.24</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="20">
         <v>0.52800000000000002</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="21">
         <v>0.52800000000000002</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="19">
         <v>0.247</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="10">
         <v>0.52800000000000002</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="11">
         <v>0.52800000000000002</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="12">
         <v>0.52800000000000002</v>
       </c>
     </row>
@@ -1392,40 +1395,40 @@
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="22">
         <v>1443.338</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="23">
         <v>1443.338</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="22">
         <v>7578.9470000000001</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="23">
         <v>7578.9470000000001</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="22">
         <v>1443.338</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="23">
         <v>1443.338</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="22">
         <v>7578.9470000000001</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="23">
         <v>7578.9470000000001</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="24">
         <v>1761.914</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="13">
         <v>7578.9470000000001</v>
       </c>
-      <c r="L8" s="18">
+      <c r="L8" s="14">
         <v>7578.9470000000001</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="15">
         <v>7578.9470000000001</v>
       </c>
     </row>
@@ -1436,37 +1439,37 @@
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="12" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1477,37 +1480,37 @@
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="12" t="s">
         <v>19</v>
       </c>
     </row>
